--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Timéo\Desktop\Matterhorn 64\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD538488-26B2-4D80-BC3D-8130A8BDC338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E1408E-3230-46C0-9D7A-411F8625E5D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E283F319-9821-4CEB-B07A-BFCD7533B832}"/>
   </bookViews>
@@ -208,15 +208,6 @@
     <t>https://www.digikey.com/en/products/detail/murata-electronics/GRM1555C1H561JA01D/702503</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/cal-chip-electronics-inc/GMC04CG380J50NT/13909763</t>
-  </si>
-  <si>
-    <t>CAP CER 38PF 50V C0G/NP0 0402</t>
-  </si>
-  <si>
-    <t>GMC04CG380J50NT</t>
-  </si>
-  <si>
     <t>C0402X5R100-474KNE-CT</t>
   </si>
   <si>
@@ -484,6 +475,15 @@
   <si>
     <t>R13,R14,R15,R16,R17,R18,R19,R20,
 R21,R22,R23,R24</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/kemet/C0402C390J5GACTU/411020</t>
+  </si>
+  <si>
+    <t>C0402C390J5GACTU</t>
+  </si>
+  <si>
+    <t>CAP CER 39PF 50V C0G/NP0 0402</t>
   </si>
 </sst>
 </file>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B6">
         <v>7</v>
@@ -1423,18 +1423,18 @@
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B7">
         <v>27</v>
@@ -1454,7 +1454,7 @@
     </row>
     <row r="8" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B8">
         <v>38</v>
@@ -1474,7 +1474,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B9">
         <v>7</v>
@@ -1494,7 +1494,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -1503,18 +1503,18 @@
         <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B11">
         <v>4</v>
@@ -1523,13 +1523,13 @@
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>151</v>
       </c>
       <c r="E11" t="s">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1554,7 +1554,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -1574,27 +1574,27 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
+        <v>142</v>
+      </c>
+      <c r="D14" t="s">
         <v>145</v>
       </c>
-      <c r="D14" t="s">
-        <v>148</v>
-      </c>
       <c r="E14" s="5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B15">
         <v>4</v>
@@ -1614,7 +1614,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B16">
         <v>2</v>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -1646,7 +1646,7 @@
         <v>45</v>
       </c>
       <c r="E17" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>46</v>
@@ -1663,18 +1663,18 @@
         <v>5051104091</v>
       </c>
       <c r="D18" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E18" s="6">
         <v>5051104091</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -1683,18 +1683,18 @@
         <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E19" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B20">
         <v>4</v>
@@ -1703,13 +1703,13 @@
         <v>21</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E20" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1723,13 +1723,13 @@
         <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E21" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1743,18 +1743,18 @@
         <v>19</v>
       </c>
       <c r="D22" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E22" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -1763,18 +1763,18 @@
         <v>31</v>
       </c>
       <c r="D23" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E23" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -1783,13 +1783,13 @@
         <v>30</v>
       </c>
       <c r="D24" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E24" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1803,18 +1803,18 @@
         <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E25" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -1823,18 +1823,18 @@
         <v>20</v>
       </c>
       <c r="D26" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E26" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -1843,18 +1843,18 @@
         <v>28</v>
       </c>
       <c r="D27" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E27" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B28">
         <v>4</v>
@@ -1863,18 +1863,18 @@
         <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E28" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B29">
         <v>12</v>
@@ -1883,18 +1883,18 @@
         <v>32</v>
       </c>
       <c r="D29" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E29" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -1903,18 +1903,18 @@
         <v>24</v>
       </c>
       <c r="D30" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E30" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -1923,18 +1923,18 @@
         <v>29</v>
       </c>
       <c r="D31" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E31" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -1943,18 +1943,18 @@
         <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E32" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B33">
         <v>2</v>
@@ -1963,18 +1963,18 @@
         <v>18</v>
       </c>
       <c r="D33" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E33" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2005,33 +2005,33 @@
         <v>1</v>
       </c>
       <c r="D37" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E37" s="6">
         <v>5051104091</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B38">
         <v>2</v>
       </c>
       <c r="C38" t="s">
+        <v>116</v>
+      </c>
+      <c r="D38" t="s">
         <v>119</v>
       </c>
-      <c r="D38" t="s">
-        <v>122</v>
-      </c>
       <c r="E38" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -2040,31 +2040,31 @@
     <hyperlink ref="F30" r:id="rId2" xr:uid="{AB95D599-6603-4622-B769-8A9F8919D4C4}"/>
     <hyperlink ref="F6" r:id="rId3" xr:uid="{84599F04-EBF6-4513-80CF-94B12FDE94AE}"/>
     <hyperlink ref="F7" r:id="rId4" xr:uid="{17824D2B-B167-4192-AE24-CFDD578032B1}"/>
-    <hyperlink ref="F8" r:id="rId5" xr:uid="{A87A8D3E-22BC-455C-AA50-2EA0602BF6E1}"/>
-    <hyperlink ref="F9" r:id="rId6" xr:uid="{9B4C5AC8-0763-47C3-B19B-6074E941995C}"/>
-    <hyperlink ref="F10" r:id="rId7" xr:uid="{BE741A20-600E-441A-B8A1-43A2D8E9017F}"/>
-    <hyperlink ref="F21" r:id="rId8" xr:uid="{AD4D64FE-FC01-453C-8627-4458226521A6}"/>
-    <hyperlink ref="F19" r:id="rId9" xr:uid="{DE6FA0D2-D8DF-4AE9-8E54-C63E6B3E96A2}"/>
-    <hyperlink ref="F18" r:id="rId10" xr:uid="{5607D1B8-9755-4656-B6CA-83C531B98F0E}"/>
-    <hyperlink ref="F20" r:id="rId11" xr:uid="{A2A5E8B8-3A4E-438B-A098-C64F0F76D70E}"/>
-    <hyperlink ref="F14" r:id="rId12" xr:uid="{EB220C62-43E2-4B0C-B41B-D5C881D9DDE3}"/>
-    <hyperlink ref="F16" r:id="rId13" xr:uid="{A4A47162-8212-4863-A797-49A9628ADD8B}"/>
-    <hyperlink ref="F13" r:id="rId14" xr:uid="{77137CB5-BFCB-48DD-AC98-09748E3373ED}"/>
-    <hyperlink ref="F12" r:id="rId15" xr:uid="{61B1DE51-6754-476F-8187-70C9005E9650}"/>
-    <hyperlink ref="F11" r:id="rId16" xr:uid="{6CD220D5-753F-4E93-B3E8-B715B9604203}"/>
-    <hyperlink ref="F23" r:id="rId17" xr:uid="{015CCB7C-A747-4157-99F8-462B7B33346B}"/>
-    <hyperlink ref="F22" r:id="rId18" xr:uid="{76601B4A-3FD4-45B9-AFFB-CDE179F3AD2B}"/>
-    <hyperlink ref="F24" r:id="rId19" xr:uid="{89169B0A-B3EB-43E6-AE9F-4B1C902EE959}"/>
-    <hyperlink ref="F25" r:id="rId20" xr:uid="{E5325364-177F-4F33-B353-FCF5A6B00A4A}"/>
-    <hyperlink ref="F26" r:id="rId21" xr:uid="{44CA85CE-58E3-43DE-8DF5-F47ECA562CBF}"/>
-    <hyperlink ref="F27" r:id="rId22" xr:uid="{7545AEAB-E719-43F1-8028-103150103B5B}"/>
-    <hyperlink ref="F28" r:id="rId23" xr:uid="{25E83C42-C777-47FA-870B-27D9DE4A8419}"/>
-    <hyperlink ref="F29" r:id="rId24" xr:uid="{C6400645-7C00-4D8F-A9EF-B756AEACF575}"/>
-    <hyperlink ref="F31" r:id="rId25" xr:uid="{6E077D76-EBD8-4243-AE14-7FFF7BC844F4}"/>
-    <hyperlink ref="F32" r:id="rId26" xr:uid="{139BBD31-6636-47DB-86AF-F8B15F0525FB}"/>
-    <hyperlink ref="F33" r:id="rId27" xr:uid="{9BF122FB-7792-4AA9-98F3-C3EADC204B5B}"/>
-    <hyperlink ref="F37" r:id="rId28" xr:uid="{E8D241DA-AB6C-40B9-83DD-171F92F8A72E}"/>
-    <hyperlink ref="F38" r:id="rId29" xr:uid="{7BAAA7F3-C728-408F-BEC2-BB780B2945E1}"/>
+    <hyperlink ref="F9" r:id="rId5" xr:uid="{9B4C5AC8-0763-47C3-B19B-6074E941995C}"/>
+    <hyperlink ref="F10" r:id="rId6" xr:uid="{BE741A20-600E-441A-B8A1-43A2D8E9017F}"/>
+    <hyperlink ref="F21" r:id="rId7" xr:uid="{AD4D64FE-FC01-453C-8627-4458226521A6}"/>
+    <hyperlink ref="F19" r:id="rId8" xr:uid="{DE6FA0D2-D8DF-4AE9-8E54-C63E6B3E96A2}"/>
+    <hyperlink ref="F18" r:id="rId9" xr:uid="{5607D1B8-9755-4656-B6CA-83C531B98F0E}"/>
+    <hyperlink ref="F20" r:id="rId10" xr:uid="{A2A5E8B8-3A4E-438B-A098-C64F0F76D70E}"/>
+    <hyperlink ref="F14" r:id="rId11" xr:uid="{EB220C62-43E2-4B0C-B41B-D5C881D9DDE3}"/>
+    <hyperlink ref="F16" r:id="rId12" xr:uid="{A4A47162-8212-4863-A797-49A9628ADD8B}"/>
+    <hyperlink ref="F13" r:id="rId13" xr:uid="{77137CB5-BFCB-48DD-AC98-09748E3373ED}"/>
+    <hyperlink ref="F12" r:id="rId14" xr:uid="{61B1DE51-6754-476F-8187-70C9005E9650}"/>
+    <hyperlink ref="F23" r:id="rId15" xr:uid="{015CCB7C-A747-4157-99F8-462B7B33346B}"/>
+    <hyperlink ref="F22" r:id="rId16" xr:uid="{76601B4A-3FD4-45B9-AFFB-CDE179F3AD2B}"/>
+    <hyperlink ref="F24" r:id="rId17" xr:uid="{89169B0A-B3EB-43E6-AE9F-4B1C902EE959}"/>
+    <hyperlink ref="F25" r:id="rId18" xr:uid="{E5325364-177F-4F33-B353-FCF5A6B00A4A}"/>
+    <hyperlink ref="F26" r:id="rId19" xr:uid="{44CA85CE-58E3-43DE-8DF5-F47ECA562CBF}"/>
+    <hyperlink ref="F27" r:id="rId20" xr:uid="{7545AEAB-E719-43F1-8028-103150103B5B}"/>
+    <hyperlink ref="F28" r:id="rId21" xr:uid="{25E83C42-C777-47FA-870B-27D9DE4A8419}"/>
+    <hyperlink ref="F29" r:id="rId22" xr:uid="{C6400645-7C00-4D8F-A9EF-B756AEACF575}"/>
+    <hyperlink ref="F31" r:id="rId23" xr:uid="{6E077D76-EBD8-4243-AE14-7FFF7BC844F4}"/>
+    <hyperlink ref="F32" r:id="rId24" xr:uid="{139BBD31-6636-47DB-86AF-F8B15F0525FB}"/>
+    <hyperlink ref="F33" r:id="rId25" xr:uid="{9BF122FB-7792-4AA9-98F3-C3EADC204B5B}"/>
+    <hyperlink ref="F37" r:id="rId26" xr:uid="{E8D241DA-AB6C-40B9-83DD-171F92F8A72E}"/>
+    <hyperlink ref="F38" r:id="rId27" xr:uid="{7BAAA7F3-C728-408F-BEC2-BB780B2945E1}"/>
+    <hyperlink ref="F8" r:id="rId28" xr:uid="{A87A8D3E-22BC-455C-AA50-2EA0602BF6E1}"/>
+    <hyperlink ref="F11" r:id="rId29" xr:uid="{D9E98AA2-5D0C-4C16-99BC-B9621ACF2C2D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId30"/>

--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Timéo\Desktop\Matterhorn 64\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E1408E-3230-46C0-9D7A-411F8625E5D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{084E8E48-6FAB-4088-9BAC-366606DAD58C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E283F319-9821-4CEB-B07A-BFCD7533B832}"/>
+    <workbookView xWindow="-28920" yWindow="2730" windowWidth="29040" windowHeight="15720" xr2:uid="{E283F319-9821-4CEB-B07A-BFCD7533B832}"/>
   </bookViews>
   <sheets>
     <sheet name="M64-Core" sheetId="1" r:id="rId1"/>
@@ -37,9 +37,6 @@
     <t>C22</t>
   </si>
   <si>
-    <t>580pF</t>
-  </si>
-  <si>
     <t>38pF</t>
   </si>
   <si>
@@ -484,6 +481,9 @@
   </si>
   <si>
     <t>CAP CER 39PF 50V C0G/NP0 0402</t>
+  </si>
+  <si>
+    <t>560pF</t>
   </si>
 </sst>
 </file>
@@ -1384,12 +1384,12 @@
   <sheetData>
     <row r="1" spans="1:6" ht="46.5" x14ac:dyDescent="0.7">
       <c r="A1" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1397,139 +1397,139 @@
         <v>0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B6">
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B7">
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
         <v>42</v>
       </c>
-      <c r="E7" t="s">
-        <v>43</v>
-      </c>
       <c r="F7" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B8">
         <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B9">
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" t="s">
         <v>53</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="E10" t="s">
-        <v>62</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B11">
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1540,81 +1540,81 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
         <v>51</v>
       </c>
-      <c r="E12" t="s">
-        <v>52</v>
-      </c>
       <c r="F12" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>5</v>
+        <v>151</v>
       </c>
       <c r="D13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="E13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
+        <v>141</v>
+      </c>
+      <c r="D14" t="s">
+        <v>144</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="D14" t="s">
-        <v>145</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B15">
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B16">
         <v>2</v>
@@ -1623,18 +1623,18 @@
         <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -1643,338 +1643,338 @@
         <v>2</v>
       </c>
       <c r="D17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" t="s">
+        <v>111</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="E17" t="s">
-        <v>112</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="6">
         <v>5051104091</v>
       </c>
       <c r="D18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E18" s="6">
         <v>5051104091</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" t="s">
         <v>79</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B20">
         <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" t="s">
         <v>70</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E23" t="s">
         <v>107</v>
       </c>
-      <c r="E23" t="s">
-        <v>108</v>
-      </c>
       <c r="F23" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D25" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25" t="s">
+        <v>93</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="E25" t="s">
-        <v>94</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E27" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B28">
         <v>4</v>
       </c>
       <c r="C28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D28" t="s">
+        <v>81</v>
+      </c>
+      <c r="E28" t="s">
         <v>82</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B29">
         <v>12</v>
       </c>
       <c r="C29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D29" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E29" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D30" t="s">
+        <v>85</v>
+      </c>
+      <c r="E30" t="s">
         <v>86</v>
       </c>
-      <c r="E30" t="s">
-        <v>87</v>
-      </c>
       <c r="F30" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D31" t="s">
+        <v>100</v>
+      </c>
+      <c r="E31" t="s">
         <v>101</v>
       </c>
-      <c r="E31" t="s">
-        <v>102</v>
-      </c>
       <c r="F31" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D32" t="s">
+        <v>88</v>
+      </c>
+      <c r="E32" t="s">
         <v>89</v>
       </c>
-      <c r="E32" t="s">
-        <v>90</v>
-      </c>
       <c r="F32" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B33">
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D33" t="s">
+        <v>66</v>
+      </c>
+      <c r="E33" t="s">
         <v>67</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1982,56 +1982,56 @@
         <v>0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D36" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="F36" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="D37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E37" s="6">
         <v>5051104091</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B38">
         <v>2</v>
       </c>
       <c r="C38" t="s">
+        <v>115</v>
+      </c>
+      <c r="D38" t="s">
+        <v>118</v>
+      </c>
+      <c r="E38" t="s">
         <v>116</v>
       </c>
-      <c r="D38" t="s">
-        <v>119</v>
-      </c>
-      <c r="E38" t="s">
+      <c r="F38" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>118</v>
       </c>
     </row>
   </sheetData>
